--- a/Excel/Payroll.xlsx
+++ b/Excel/Payroll.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnyan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c3f59aaaf5f4e1f8/Desktop/Data-analysis/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A294D9C-541A-428F-8219-342C679DF6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{2CFDBAE4-3FF6-4C49-801A-99A4E4C3A217}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2CFDBAE4-3FF6-4C49-801A-99A4E4C3A217}"/>
   </bookViews>
   <sheets>
     <sheet name="Payroll" sheetId="2" r:id="rId1"/>
@@ -214,7 +214,7 @@
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3601,44 +3601,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2548A2-F24F-4E11-9AF6-0431174A6F4E}">
   <dimension ref="A1:AD34"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.8984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.09765625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="12" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="12" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.8984375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.8984375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3674,7 +3674,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:30">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AD3" s="15"/>
     </row>
-    <row r="4" spans="1:30">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>3219.75</v>
       </c>
     </row>
-    <row r="5" spans="1:30">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -4001,7 +4001,7 @@
         <v>2157</v>
       </c>
     </row>
-    <row r="6" spans="1:30">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>3635.4500000000007</v>
       </c>
     </row>
-    <row r="7" spans="1:30">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -4221,7 +4221,7 @@
         <v>4343.25</v>
       </c>
     </row>
-    <row r="8" spans="1:30">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -4331,7 +4331,7 @@
         <v>1755.7</v>
       </c>
     </row>
-    <row r="9" spans="1:30">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>3118.7999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:30">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>5497</v>
       </c>
     </row>
-    <row r="11" spans="1:30">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>3111.5</v>
       </c>
     </row>
-    <row r="12" spans="1:30">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -4771,7 +4771,7 @@
         <v>2847.7</v>
       </c>
     </row>
-    <row r="13" spans="1:30">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -4881,7 +4881,7 @@
         <v>2833.9</v>
       </c>
     </row>
-    <row r="14" spans="1:30">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -4991,7 +4991,7 @@
         <v>2366.8000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:30">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>2111.3000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:30">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -5211,7 +5211,7 @@
         <v>1906.5</v>
       </c>
     </row>
-    <row r="17" spans="1:30">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>1756.4399999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:30">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -5431,7 +5431,7 @@
         <v>2880</v>
       </c>
     </row>
-    <row r="19" spans="1:30">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -5541,7 +5541,7 @@
         <v>9153.5</v>
       </c>
     </row>
-    <row r="20" spans="1:30">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>7950</v>
       </c>
     </row>
-    <row r="22" spans="1:30">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>37</v>
       </c>
@@ -5764,7 +5764,7 @@
         <v>9153.5</v>
       </c>
     </row>
-    <row r="23" spans="1:30">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -5877,7 +5877,7 @@
         <v>1755.7</v>
       </c>
     </row>
-    <row r="24" spans="1:30">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -5990,7 +5990,7 @@
         <v>3567.3288235294126</v>
       </c>
     </row>
-    <row r="25" spans="1:30">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -6103,7 +6103,7 @@
         <v>60644.590000000011</v>
       </c>
     </row>
-    <row r="34" spans="10:10">
+    <row r="34" spans="10:10" x14ac:dyDescent="0.3">
       <c r="J34">
         <v>6</v>
       </c>
@@ -6117,21 +6117,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D997FC4B-49C3-4B6D-BDBF-47BBA35BB0A4}">
   <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.796875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.69921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.69921875" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="5.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.44140625" style="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="5.44140625" style="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="73.8">
+    <row r="1" spans="1:14" ht="95.4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>45</v>
       </c>
@@ -6165,7 +6165,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>50</v>
       </c>
@@ -6182,7 +6182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="14.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -6190,7 +6190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -6210,19 +6210,19 @@
         <v>1</v>
       </c>
       <c r="I4" s="16">
-        <f>D4/D$2</f>
+        <f t="shared" ref="I4:I20" si="0">D4/D$2</f>
         <v>1</v>
       </c>
       <c r="J4" s="16">
-        <f>E4/E$2</f>
+        <f t="shared" ref="J4:J20" si="1">E4/E$2</f>
         <v>0.95</v>
       </c>
       <c r="K4" s="16">
-        <f>F4/F$2</f>
+        <f t="shared" ref="K4:K20" si="2">F4/F$2</f>
         <v>0.93</v>
       </c>
       <c r="L4" s="16">
-        <f>G4/G$2</f>
+        <f t="shared" ref="L4:L20" si="3">G4/G$2</f>
         <v>1</v>
       </c>
       <c r="N4" s="16" t="b">
@@ -6230,7 +6230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -6250,27 +6250,27 @@
         <v>1</v>
       </c>
       <c r="I5" s="16">
-        <f>D5/D$2</f>
+        <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
       <c r="J5" s="16">
-        <f>E5/E$2</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K5" s="16">
-        <f>F5/F$2</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L5" s="16">
-        <f>G5/G$2</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N5" s="16" t="b">
-        <f t="shared" ref="N5:N20" si="0">OR(I5&lt;0.5,J5&lt;0.5,K5&lt;0.5,L5&lt;0.5)</f>
+        <f t="shared" ref="N5:N20" si="4">OR(I5&lt;0.5,J5&lt;0.5,K5&lt;0.5,L5&lt;0.5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -6290,27 +6290,27 @@
         <v>1</v>
       </c>
       <c r="I6" s="16">
-        <f>D6/D$2</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="J6" s="16">
-        <f>E6/E$2</f>
+        <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
       <c r="K6" s="16">
-        <f>F6/F$2</f>
+        <f t="shared" si="2"/>
         <v>0.82</v>
       </c>
       <c r="L6" s="16">
-        <f>G6/G$2</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N6" s="16" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -6330,27 +6330,27 @@
         <v>1</v>
       </c>
       <c r="I7" s="16">
-        <f>D7/D$2</f>
+        <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
       <c r="J7" s="16">
-        <f>E7/E$2</f>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K7" s="16">
-        <f>F7/F$2</f>
+        <f t="shared" si="2"/>
         <v>0.73</v>
       </c>
       <c r="L7" s="16">
-        <f>G7/G$2</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N7" s="16" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -6370,27 +6370,27 @@
         <v>1</v>
       </c>
       <c r="I8" s="16">
-        <f>D8/D$2</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J8" s="16">
-        <f>E8/E$2</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K8" s="16">
-        <f>F8/F$2</f>
+        <f t="shared" si="2"/>
         <v>0.59</v>
       </c>
       <c r="L8" s="16">
-        <f>G8/G$2</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N8" s="16" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -6410,27 +6410,27 @@
         <v>1</v>
       </c>
       <c r="I9" s="16">
-        <f>D9/D$2</f>
+        <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
       <c r="J9" s="16">
-        <f>E9/E$2</f>
+        <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
       <c r="K9" s="16">
-        <f>F9/F$2</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L9" s="16">
-        <f>G9/G$2</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N9" s="16" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -6450,187 +6450,187 @@
         <v>0</v>
       </c>
       <c r="I10" s="16">
-        <f>D10/D$2</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="J10" s="16">
-        <f>E10/E$2</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K10" s="16">
-        <f>F10/F$2</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="L10" s="16">
-        <f>G10/G$2</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N10" s="16" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11">
+        <v>100</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="I11" s="16">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="J11" s="16">
+        <f t="shared" si="1"/>
+        <v>0.3</v>
+      </c>
+      <c r="K11" s="16">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L11" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N11" s="16" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>67</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="I12" s="16">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="J12" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="16">
+        <f t="shared" si="2"/>
+        <v>0.67</v>
+      </c>
+      <c r="L12" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N12" s="16" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13">
+        <v>9</v>
+      </c>
+      <c r="E13">
+        <v>20</v>
+      </c>
+      <c r="F13">
+        <v>70</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="I13" s="16">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="J13" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K13" s="16">
+        <f t="shared" si="2"/>
+        <v>0.7</v>
+      </c>
+      <c r="L13" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N13" s="16" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14">
         <v>19</v>
       </c>
-      <c r="D11">
-        <v>5</v>
-      </c>
-      <c r="E11">
-        <v>6</v>
-      </c>
-      <c r="F11">
-        <v>100</v>
-      </c>
-      <c r="G11">
+      <c r="F14">
+        <v>80</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
-      <c r="I11" s="16">
-        <f>D11/D$2</f>
-        <v>0.5</v>
-      </c>
-      <c r="J11" s="16">
-        <f>E11/E$2</f>
-        <v>0.3</v>
-      </c>
-      <c r="K11" s="16">
-        <f>F11/F$2</f>
-        <v>1</v>
-      </c>
-      <c r="L11" s="16">
-        <f>G11/G$2</f>
-        <v>1</v>
-      </c>
-      <c r="N11" s="16" t="b">
+      <c r="I14" s="16">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="J14" s="16">
+        <f t="shared" si="1"/>
+        <v>0.95</v>
+      </c>
+      <c r="K14" s="16">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="L14" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N14" s="16" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-      <c r="E12">
-        <v>20</v>
-      </c>
-      <c r="F12">
-        <v>67</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="I12" s="16">
-        <f>D12/D$2</f>
-        <v>1</v>
-      </c>
-      <c r="J12" s="16">
-        <f>E12/E$2</f>
-        <v>1</v>
-      </c>
-      <c r="K12" s="16">
-        <f>F12/F$2</f>
-        <v>0.67</v>
-      </c>
-      <c r="L12" s="16">
-        <f>G12/G$2</f>
-        <v>1</v>
-      </c>
-      <c r="N12" s="16" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13">
-        <v>9</v>
-      </c>
-      <c r="E13">
-        <v>20</v>
-      </c>
-      <c r="F13">
-        <v>70</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="I13" s="16">
-        <f>D13/D$2</f>
-        <v>0.9</v>
-      </c>
-      <c r="J13" s="16">
-        <f>E13/E$2</f>
-        <v>1</v>
-      </c>
-      <c r="K13" s="16">
-        <f>F13/F$2</f>
-        <v>0.7</v>
-      </c>
-      <c r="L13" s="16">
-        <f>G13/G$2</f>
-        <v>1</v>
-      </c>
-      <c r="N13" s="16" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14">
-        <v>10</v>
-      </c>
-      <c r="E14">
-        <v>19</v>
-      </c>
-      <c r="F14">
-        <v>80</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="I14" s="16">
-        <f>D14/D$2</f>
-        <v>1</v>
-      </c>
-      <c r="J14" s="16">
-        <f>E14/E$2</f>
-        <v>0.95</v>
-      </c>
-      <c r="K14" s="16">
-        <f>F14/F$2</f>
-        <v>0.8</v>
-      </c>
-      <c r="L14" s="16">
-        <f>G14/G$2</f>
-        <v>1</v>
-      </c>
-      <c r="N14" s="16" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -6650,27 +6650,27 @@
         <v>1</v>
       </c>
       <c r="I15" s="16">
-        <f>D15/D$2</f>
+        <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
       <c r="J15" s="16">
-        <f>E15/E$2</f>
+        <f t="shared" si="1"/>
         <v>0.85</v>
       </c>
       <c r="K15" s="16">
-        <f>F15/F$2</f>
+        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="L15" s="16">
-        <f>G15/G$2</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N15" s="16" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>28</v>
       </c>
@@ -6690,107 +6690,107 @@
         <v>0</v>
       </c>
       <c r="I16" s="16">
-        <f>D16/D$2</f>
+        <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
       <c r="J16" s="16">
-        <f>E16/E$2</f>
+        <f t="shared" si="1"/>
         <v>0.95</v>
       </c>
       <c r="K16" s="16">
-        <f>F16/F$2</f>
+        <f t="shared" si="2"/>
         <v>0.45</v>
       </c>
       <c r="L16" s="16">
-        <f>G16/G$2</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N16" s="16" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17">
+        <v>7</v>
+      </c>
+      <c r="E17">
+        <v>20</v>
+      </c>
+      <c r="F17">
+        <v>90</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="I17" s="16">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="J17" s="16">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K17" s="16">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+      <c r="L17" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N17" s="16" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18">
+        <v>80</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="I18" s="16">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
+      <c r="J18" s="16">
+        <f t="shared" si="1"/>
+        <v>0.5</v>
+      </c>
+      <c r="K18" s="16">
+        <f t="shared" si="2"/>
+        <v>0.8</v>
+      </c>
+      <c r="L18" s="16">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="N18" s="16" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17">
-        <v>7</v>
-      </c>
-      <c r="E17">
-        <v>20</v>
-      </c>
-      <c r="F17">
-        <v>90</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="I17" s="16">
-        <f>D17/D$2</f>
-        <v>0.7</v>
-      </c>
-      <c r="J17" s="16">
-        <f>E17/E$2</f>
-        <v>1</v>
-      </c>
-      <c r="K17" s="16">
-        <f>F17/F$2</f>
-        <v>0.9</v>
-      </c>
-      <c r="L17" s="16">
-        <f>G17/G$2</f>
-        <v>1</v>
-      </c>
-      <c r="N17" s="16" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18">
-        <v>10</v>
-      </c>
-      <c r="E18">
-        <v>10</v>
-      </c>
-      <c r="F18">
-        <v>80</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="I18" s="16">
-        <f>D18/D$2</f>
-        <v>1</v>
-      </c>
-      <c r="J18" s="16">
-        <f>E18/E$2</f>
-        <v>0.5</v>
-      </c>
-      <c r="K18" s="16">
-        <f>F18/F$2</f>
-        <v>0.8</v>
-      </c>
-      <c r="L18" s="16">
-        <f>G18/G$2</f>
-        <v>1</v>
-      </c>
-      <c r="N18" s="16" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -6810,27 +6810,27 @@
         <v>1</v>
       </c>
       <c r="I19" s="16">
-        <f>D19/D$2</f>
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="J19" s="16">
-        <f>E19/E$2</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="K19" s="16">
-        <f>F19/F$2</f>
+        <f t="shared" si="2"/>
         <v>0.69</v>
       </c>
       <c r="L19" s="16">
-        <f>G19/G$2</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N19" s="16" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -6850,27 +6850,27 @@
         <v>1</v>
       </c>
       <c r="I20" s="16">
-        <f>D20/D$2</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="J20" s="16">
-        <f>E20/E$2</f>
+        <f t="shared" si="1"/>
         <v>0.7</v>
       </c>
       <c r="K20" s="16">
-        <f>F20/F$2</f>
+        <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
       <c r="L20" s="16">
-        <f>G20/G$2</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="N20" s="16" t="b">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>52</v>
       </c>
@@ -6907,7 +6907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -6944,7 +6944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -7041,7 +7041,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45BA60B1-EC95-4111-8FEA-63D92339ADDC}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Excel/Payroll.xlsx
+++ b/Excel/Payroll.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A294D9C-541A-428F-8219-342C679DF6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{2CFDBAE4-3FF6-4C49-801A-99A4E4C3A217}"/>
+    <workbookView minimized="1" xWindow="5868" yWindow="0" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{2CFDBAE4-3FF6-4C49-801A-99A4E4C3A217}"/>
   </bookViews>
   <sheets>
     <sheet name="Payroll" sheetId="2" r:id="rId1"/>
